--- a/day-2/day-2.xlsx
+++ b/day-2/day-2.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Note" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Question" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -19,16 +20,150 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+  <si>
+    <t xml:space="preserve">1. Excel được dùng để thu thập, làm sạch, phân tích dữ liệu và tạo báo cáo nhanh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Dataset trong Excel: Mỗi column đại diện cho một thuộc tính, mỗi row là một record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Data types: Text, Date, Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Sort là sắp xếp dữ liệu, có thể sort tăng dần/giảm dần/theo ngày/theo alphabet. Filter không xóa dữ liệu chỉ lọc dòng bạn muốn xem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Nguyên tắc quan trọng: đừng sửa dữ liệu gốc một cách tùy tiện, tốt nhất là nên tạo file mới, vì sửa trực tiếp bị sai rất khó để quay lại bản gốc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Excel có phân biệt hoa thường, có quantity = -1 thì chưa chắc là data sai cần hiểu business rule trước, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laptop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xác định data type hợp lý cho từng column:
+ Order ID: Date: Product: Region: Quantity: Price: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Có những vấn đề dữ liệu nào bạn phát hiện được? 
+Liệt kê từng vấn đề và giải thích</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nếu tạo thêm column Revenue, công thức Excel là gì?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không cần tính bằng Excel, hãy tính total revenue bằng tay. Revenue = Quantity × Price </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager hỏi:  Tôi muốn xem riêng các đơn hàng ở South.  
+Bạn sẽ dùng Sort hay Filter? Tại sao?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dòng này:  O004 | 02/09/2026 | Keyboard | South | -1 | 1000000  
+Bạn có xóa nó ngay không?  Nếu không, bạn sẽ làm gì trước?</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -45,16 +180,37 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <u val="single"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -62,6 +218,13 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -88,9 +251,37 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -110,9 +301,40 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -121,4 +343,235 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>22000000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/day-2/day-2.xlsx
+++ b/day-2/day-2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
   <si>
     <t xml:space="preserve">1. Excel được dùng để thu thập, làm sạch, phân tích dữ liệu và tạo báo cáo nhanh</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t xml:space="preserve">Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
   </si>
   <si>
     <t xml:space="preserve">O001</t>
@@ -117,6 +120,9 @@
  Order ID: Date: Product: Region: Quantity: Price: </t>
   </si>
   <si>
+    <t xml:space="preserve">order id: text, date: Date, product: Text, Region: Text, quantity: Number, Price: Number</t>
+  </si>
+  <si>
     <t xml:space="preserve">Task 2</t>
   </si>
   <si>
@@ -124,10 +130,16 @@
 Liệt kê từng vấn đề và giải thích</t>
   </si>
   <si>
+    <t xml:space="preserve">quantity có giá trị -1, region có bản ghi trống, Ở Region có sự không nhất quán về cách viết (hoa thường không thống nhất)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Task 3</t>
   </si>
   <si>
     <t xml:space="preserve">Nếu tạo thêm column Revenue, công thức Excel là gì?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tạo column và dùng công thức Revenue = Quantity x Price, lấy giá trị cột E nhân với cột F</t>
   </si>
   <si>
     <t xml:space="preserve">Task 4</t>
@@ -143,11 +155,17 @@
 Bạn sẽ dùng Sort hay Filter? Tại sao?</t>
   </si>
   <si>
+    <t xml:space="preserve">dùng Filter vì đây chỉ muốn xem riêng đơn hàng ở South</t>
+  </si>
+  <si>
     <t xml:space="preserve">Task 6</t>
   </si>
   <si>
     <t xml:space="preserve">Dòng này:  O004 | 02/09/2026 | Keyboard | South | -1 | 1000000  
 Bạn có xóa nó ngay không?  Nếu không, bạn sẽ làm gì trước?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không xóa, vì chưa rõ business như nào</t>
   </si>
 </sst>
 </file>
@@ -158,7 +176,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -189,8 +207,21 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
       <u val="single"/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC9211E"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -251,7 +282,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -260,6 +291,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -272,12 +307,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -293,6 +332,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FFC9211E"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -350,7 +449,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -372,198 +471,244 @@
       <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="D2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>20000000</v>
       </c>
+      <c r="G2" s="3" t="n">
+        <f aca="false">E2*F2</f>
+        <v>20000000</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <f aca="false">E3*F3</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <f aca="false">E4*F4</f>
+        <v>22000000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <f aca="false">E5*F5</f>
+        <v>-1000000</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <f aca="false">E6*F6</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <f aca="false">E7*F7</f>
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>500000</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>22000000</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="G8" s="3" t="n">
+        <f aca="false">E8*F8</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="I10" s="8" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>33</v>
+      <c r="A12" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>35</v>
+      <c r="A13" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="6" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
+      <c r="A16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
+      <c r="A17" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/day-2/day-2.xlsx
+++ b/day-2/day-2.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Question" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Exercise" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="65">
   <si>
     <t xml:space="preserve">1. Excel được dùng để thu thập, làm sạch, phân tích dữ liệu và tạo báo cáo nhanh</t>
   </si>
@@ -39,6 +40,28 @@
   </si>
   <si>
     <t xml:space="preserve">6. Excel có phân biệt hoa thường, có quantity = -1 thì chưa chắc là data sai cần hiểu business rule trước, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Data handling:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open file
+       ↓
+2. Kiểm tra columns
+       ↓
+3. Xác định mỗi row đại diện cho cái gì
+       ↓
+4. Kiểm tra data types
+       ↓
+5. Kiểm tra missing values
+       ↓
+6. Kiểm tra duplicate
+       ↓
+7. Kiểm tra giá trị bất thường
+       ↓
+8. Chuẩn hóa dữ liệu nếu cần
+       ↓
+9. Bắt đầu phân tích</t>
   </si>
   <si>
     <t xml:space="preserve">Order ID</t>
@@ -166,6 +189,56 @@
   </si>
   <si>
     <t xml:space="preserve">Không xóa, vì chưa rõ business như nào</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn sẽ kiểm tra những gì trước khi bắt đầu tính revenue theo Region?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kiểm tra data type của các column, có giá trị nào bất thường không, có bị thiếu dữ liệu ô nào không, có business rule nào lạ không, Granularity của dataset, giá trị có nhất quán không (hoa thường nhất quán,..)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nếu manager yêu cầu:      "Chỉ xem những đơn hàng ở South"  Bạn dùng công cụ nào?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter theo Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nếu muốn tìm các record có Quantity &lt; 0, bạn dùng Excel Filter như thế nào?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter ghi điều kiện &lt; 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tại sao North và north có thể gây vấn đề khi phân tích?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel phân biệt nó thành 2 giá trị khác nhau, nên ảnh hưởng đến kết quả tính toán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nếu dataset có 50.000 dòng, tại sao Freeze Top Row hữu ích?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">làm vậy thì header sẽ cố định, chỉ cuộn được giá trị thôi, nên dễ theo dõi các record để hiểu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager hỏi:      "North có revenue bao nhiêu?"  
+Bạn thấy:  North north  Bạn có cộng cả hai ngay không?  
+Hãy giải thích cách bạn xử lý trước khi tính.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tôi sẽ hỏi lại vì sao có sự khác nhau này, nếu nó chỉ là lỗi do nhập liệu thì format về cùng dạng rồi tính</t>
   </si>
 </sst>
 </file>
@@ -176,7 +249,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -199,8 +272,8 @@
       <family val="0"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
+      <color rgb="FFC9211E"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -210,18 +283,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <u val="single"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFC9211E"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -282,45 +349,65 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -400,37 +487,47 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="192.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -453,262 +550,447 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>20000000</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <f aca="false">E2*F2</f>
         <v>20000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>500000</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="4" t="n">
         <f aca="false">E3*F3</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="B4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>22000000</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="4" t="n">
         <f aca="false">E4*F4</f>
         <v>22000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>1000000</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="4" t="n">
         <f aca="false">E5*F5</f>
         <v>-1000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="3" t="n">
+      <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>500000</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <f aca="false">E6*F6</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="3" t="n">
+      <c r="A7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>20000000</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <f aca="false">E7*F7</f>
         <v>20000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="3" t="n">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
         <v>500000</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="4" t="n">
         <f aca="false">E8*F8</f>
         <v>1500000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="8" t="s">
+    <row r="10" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="I10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="8" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
         <v>35</v>
       </c>
+      <c r="B11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>36</v>
+      <c r="A12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="11.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
+      <c r="B13" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
